--- a/asignaturas.xlsx
+++ b/asignaturas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ildeberto/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D46CCCB6-5F1E-A94C-A6D1-CCD22AC64670}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD70D3BF-F346-D64A-960F-1672F1B15511}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="36000" windowHeight="24000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="36000" windowHeight="21700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="106">
   <si>
     <t>SEMESTRE</t>
   </si>
@@ -260,9 +260,6 @@
   </si>
   <si>
     <t>ENE-JUN/2014</t>
-  </si>
-  <si>
-    <t>MAESTRÍA</t>
   </si>
   <si>
     <t>AGO-DIC/2014</t>
@@ -465,7 +462,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -480,30 +477,29 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -833,269 +829,269 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" s="21" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="20" t="s">
+    <row r="2" spans="1:4" s="20" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" s="20" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="B3" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="B2" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="D2" s="20" t="s">
+      <c r="C3" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" s="20" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" s="20" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" s="18" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" s="18" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="D7" s="17" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="1:4" s="21" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="20" t="s">
+    <row r="8" spans="1:4" s="18" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" s="18" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" s="18" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" s="14" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" s="14" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" s="14" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" s="14" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" s="14" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="D16" s="15" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="B17" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="C17" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="D18" s="15" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="B19" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="C3" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="D3" s="20" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" s="21" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="20" t="s">
-        <v>94</v>
-      </c>
-      <c r="B4" s="20" t="s">
-        <v>100</v>
-      </c>
-      <c r="C4" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="D4" s="20" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" s="21" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="20" t="s">
-        <v>94</v>
-      </c>
-      <c r="B5" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="C5" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="D5" s="20" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" s="19" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="D6" s="18" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" s="19" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="B7" s="18" t="s">
-        <v>99</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="D7" s="18" t="s">
+      <c r="C19" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="D19" s="15" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="8" spans="1:4" s="19" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="B8" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="D8" s="18" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" s="19" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="B9" s="18" t="s">
+    <row r="20" spans="1:4" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="B20" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="D9" s="18" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" s="19" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="B10" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="D10" s="18" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="D11" s="14" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="B12" s="14" t="s">
-        <v>97</v>
-      </c>
-      <c r="C12" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="D12" s="14" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="B13" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="C13" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="D13" s="14" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="B14" s="14" t="s">
-        <v>98</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="D14" s="14" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="B15" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C15" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="D15" s="14" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" s="17" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="B16" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="C16" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="D16" s="16" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" s="17" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="B17" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="C17" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="D17" s="16" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" s="17" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="B18" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="C18" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="D18" s="16" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" s="17" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="B19" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="C19" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="D19" s="16" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" s="17" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="B20" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="C20" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="D20" s="16" t="s">
+      <c r="C20" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="D20" s="15" t="s">
         <v>54</v>
       </c>
     </row>
@@ -1451,10 +1447,10 @@
     </row>
     <row r="46" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A46" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B46" s="7" t="s">
         <v>85</v>
-      </c>
-      <c r="B46" s="7" t="s">
-        <v>86</v>
       </c>
       <c r="C46" s="7" t="s">
         <v>52</v>
@@ -1465,10 +1461,10 @@
     </row>
     <row r="47" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A47" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B47" s="7" t="s">
         <v>85</v>
-      </c>
-      <c r="B47" s="7" t="s">
-        <v>86</v>
       </c>
       <c r="C47" s="7" t="s">
         <v>52</v>
@@ -1479,7 +1475,7 @@
     </row>
     <row r="48" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A48" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B48" s="7" t="s">
         <v>41</v>
@@ -1493,13 +1489,13 @@
     </row>
     <row r="49" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A49" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B49" s="7" t="s">
         <v>28</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="D49" s="7" t="s">
         <v>54</v>
@@ -1555,7 +1551,7 @@
         <v>28</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="D53" s="6" t="s">
         <v>54</v>
@@ -1563,7 +1559,7 @@
     </row>
     <row r="54" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>37</v>
@@ -1577,7 +1573,7 @@
     </row>
     <row r="55" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>29</v>
@@ -1591,7 +1587,7 @@
     </row>
     <row r="56" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>37</v>
@@ -1605,13 +1601,13 @@
     </row>
     <row r="57" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>54</v>
@@ -1619,7 +1615,7 @@
     </row>
     <row r="58" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A58" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>37</v>
@@ -1633,7 +1629,7 @@
     </row>
     <row r="59" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A59" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>31</v>
@@ -1647,7 +1643,7 @@
     </row>
     <row r="60" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A60" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>41</v>
@@ -1661,13 +1657,13 @@
     </row>
     <row r="61" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A61" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="D61" s="5" t="s">
         <v>54</v>
@@ -1675,7 +1671,7 @@
     </row>
     <row r="62" spans="1:4" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A62" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B62" s="11" t="s">
         <v>29</v>
@@ -1689,13 +1685,13 @@
     </row>
     <row r="63" spans="1:4" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A63" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B63" s="11" t="s">
         <v>28</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="D63" s="11" t="s">
         <v>54</v>
@@ -1703,7 +1699,7 @@
     </row>
     <row r="64" spans="1:4" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A64" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B64" s="11" t="s">
         <v>48</v>
@@ -1712,12 +1708,12 @@
         <v>52</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="65" spans="1:4" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A65" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B65" s="11" t="s">
         <v>37</v>
@@ -1779,7 +1775,7 @@
         <v>28</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>54</v>
@@ -2571,7 +2567,7 @@
     </row>
     <row r="126" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A126" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B126" s="6" t="s">
         <v>46</v>
@@ -2585,7 +2581,7 @@
     </row>
     <row r="127" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A127" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B127" s="6" t="s">
         <v>45</v>
@@ -2599,7 +2595,7 @@
     </row>
     <row r="128" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A128" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B128" s="6" t="s">
         <v>48</v>
@@ -2613,7 +2609,7 @@
     </row>
     <row r="129" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A129" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B129" s="6" t="s">
         <v>38</v>
@@ -2711,7 +2707,7 @@
     </row>
     <row r="136" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A136" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B136" s="5" t="s">
         <v>46</v>
@@ -2725,7 +2721,7 @@
     </row>
     <row r="137" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A137" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B137" s="5" t="s">
         <v>45</v>
@@ -2739,7 +2735,7 @@
     </row>
     <row r="138" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A138" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B138" s="5" t="s">
         <v>48</v>
@@ -2753,7 +2749,7 @@
     </row>
     <row r="139" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A139" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B139" s="5" t="s">
         <v>61</v>
@@ -2767,7 +2763,7 @@
     </row>
     <row r="140" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A140" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B140" s="5" t="s">
         <v>38</v>
@@ -2779,7 +2775,7 @@
         <v>59</v>
       </c>
       <c r="E140" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="141" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.2">
@@ -2821,7 +2817,7 @@
         <v>52</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="144" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.2">
@@ -2838,12 +2834,12 @@
         <v>59</v>
       </c>
       <c r="E144" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="145" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A145" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B145" s="3" t="s">
         <v>38</v>
@@ -2855,12 +2851,12 @@
         <v>59</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="146" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A146" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B146" s="3" t="s">
         <v>42</v>
@@ -2874,7 +2870,7 @@
     </row>
     <row r="147" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A147" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B147" s="3" t="s">
         <v>49</v>
@@ -2928,12 +2924,12 @@
         <v>59</v>
       </c>
       <c r="E150" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="151" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A151" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B151" s="7" t="s">
         <v>38</v>
@@ -2973,12 +2969,12 @@
         <v>59</v>
       </c>
       <c r="E153" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="154" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A154" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B154" s="2" t="s">
         <v>50</v>
@@ -2990,12 +2986,12 @@
         <v>59</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="155" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A155" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B155" s="2" t="s">
         <v>38</v>
@@ -3009,10 +3005,10 @@
     </row>
     <row r="156" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A156" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>52</v>
@@ -3021,12 +3017,12 @@
         <v>59</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="157" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A157" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B157" s="2" t="s">
         <v>46</v>
@@ -3052,7 +3048,7 @@
         <v>59</v>
       </c>
       <c r="E158" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="159" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -3097,7 +3093,7 @@
         <v>59</v>
       </c>
       <c r="E161" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="162" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.2">
@@ -3142,7 +3138,7 @@
         <v>59</v>
       </c>
       <c r="E164" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="165" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.2">
@@ -3173,7 +3169,7 @@
         <v>59</v>
       </c>
       <c r="E166" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="167" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.2">
@@ -3190,43 +3186,43 @@
         <v>59</v>
       </c>
     </row>
-    <row r="168" spans="1:6" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A168" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="B168" s="12" t="s">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A168" t="s">
+        <v>88</v>
+      </c>
+      <c r="B168" t="s">
         <v>48</v>
       </c>
-      <c r="C168" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="D168" s="12" t="s">
+      <c r="C168" t="s">
+        <v>52</v>
+      </c>
+      <c r="D168" t="s">
         <v>67</v>
       </c>
-      <c r="E168" s="13">
+      <c r="E168" s="12">
         <v>35977</v>
       </c>
-      <c r="F168" s="13">
+      <c r="F168" s="12">
         <v>36012</v>
       </c>
     </row>
-    <row r="169" spans="1:6" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A169" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="B169" s="12" t="s">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A169" t="s">
+        <v>88</v>
+      </c>
+      <c r="B169" t="s">
         <v>45</v>
       </c>
-      <c r="C169" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="D169" s="12" t="s">
+      <c r="C169" t="s">
+        <v>52</v>
+      </c>
+      <c r="D169" t="s">
         <v>67</v>
       </c>
-      <c r="E169" s="13">
+      <c r="E169" s="12">
         <v>35977</v>
       </c>
-      <c r="F169" s="13">
+      <c r="F169" s="12">
         <v>36012</v>
       </c>
     </row>

--- a/asignaturas.xlsx
+++ b/asignaturas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10426"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ildeberto/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ildeberto/Desktop/Recopilacion/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD70D3BF-F346-D64A-960F-1672F1B15511}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C9E6BD7-AE42-EB44-A4AC-16CFD723965A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="36000" windowHeight="21700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="36000" windowHeight="21600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="825" uniqueCount="122">
   <si>
     <t>SEMESTRE</t>
   </si>
@@ -283,15 +283,9 @@
     <t>Programación I</t>
   </si>
   <si>
-    <t>2gpos?</t>
-  </si>
-  <si>
     <t>VERANO 1998</t>
   </si>
   <si>
-    <t>*</t>
-  </si>
-  <si>
     <t>ENE-JUN/2024</t>
   </si>
   <si>
@@ -338,6 +332,60 @@
   </si>
   <si>
     <t>FEB-JUN/2000</t>
+  </si>
+  <si>
+    <t>VERANO 2000</t>
+  </si>
+  <si>
+    <t>FEB-JUN/1998</t>
+  </si>
+  <si>
+    <t>Sistemas Digitales II</t>
+  </si>
+  <si>
+    <t>FEB-JUN/1996</t>
+  </si>
+  <si>
+    <t>Fundamentos de Análisis Numérico</t>
+  </si>
+  <si>
+    <t>AGO-DIC/1995</t>
+  </si>
+  <si>
+    <t>Matemáticas 2</t>
+  </si>
+  <si>
+    <t>Matemáticas 1</t>
+  </si>
+  <si>
+    <t>VERANO 1999</t>
+  </si>
+  <si>
+    <t>VERANO 1996</t>
+  </si>
+  <si>
+    <t>VERANO 1997</t>
+  </si>
+  <si>
+    <t>AGO-DIC/1996</t>
+  </si>
+  <si>
+    <t>VERANO 2002</t>
+  </si>
+  <si>
+    <t>FEB-JUN/1997</t>
+  </si>
+  <si>
+    <t>AGO-DIC/1997</t>
+  </si>
+  <si>
+    <t>FEB-JUN/2010</t>
+  </si>
+  <si>
+    <t>VERANO/2008</t>
+  </si>
+  <si>
+    <t>ENE-JUN/2009</t>
   </si>
 </sst>
 </file>
@@ -373,7 +421,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -434,6 +482,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -462,7 +522,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -502,6 +562,8 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -806,7 +868,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F169"/>
+  <dimension ref="A1:F207"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
@@ -831,7 +893,7 @@
     </row>
     <row r="2" spans="1:4" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B2" s="19" t="s">
         <v>26</v>
@@ -845,10 +907,10 @@
     </row>
     <row r="3" spans="1:4" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="19" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C3" s="19" t="s">
         <v>51</v>
@@ -859,10 +921,10 @@
     </row>
     <row r="4" spans="1:4" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A4" s="19" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C4" s="19" t="s">
         <v>51</v>
@@ -873,10 +935,10 @@
     </row>
     <row r="5" spans="1:4" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="19" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C5" s="19" t="s">
         <v>52</v>
@@ -887,7 +949,7 @@
     </row>
     <row r="6" spans="1:4" s="18" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="17" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B6" s="17" t="s">
         <v>28</v>
@@ -901,10 +963,10 @@
     </row>
     <row r="7" spans="1:4" s="18" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A7" s="17" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C7" s="17" t="s">
         <v>51</v>
@@ -915,10 +977,10 @@
     </row>
     <row r="8" spans="1:4" s="18" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8" s="17" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C8" s="17" t="s">
         <v>52</v>
@@ -929,7 +991,7 @@
     </row>
     <row r="9" spans="1:4" s="18" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A9" s="17" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B9" s="17" t="s">
         <v>30</v>
@@ -943,7 +1005,7 @@
     </row>
     <row r="10" spans="1:4" s="18" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A10" s="17" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B10" s="17" t="s">
         <v>30</v>
@@ -957,7 +1019,7 @@
     </row>
     <row r="11" spans="1:4" s="14" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A11" s="13" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B11" s="13" t="s">
         <v>32</v>
@@ -971,10 +1033,10 @@
     </row>
     <row r="12" spans="1:4" s="14" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A12" s="13" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C12" s="13" t="s">
         <v>51</v>
@@ -985,7 +1047,7 @@
     </row>
     <row r="13" spans="1:4" s="14" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A13" s="13" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B13" s="13" t="s">
         <v>28</v>
@@ -999,10 +1061,10 @@
     </row>
     <row r="14" spans="1:4" s="14" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A14" s="13" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C14" s="13" t="s">
         <v>52</v>
@@ -1013,7 +1075,7 @@
     </row>
     <row r="15" spans="1:4" s="14" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A15" s="13" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B15" s="13" t="s">
         <v>30</v>
@@ -1027,7 +1089,7 @@
     </row>
     <row r="16" spans="1:4" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A16" s="15" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B16" s="15" t="s">
         <v>85</v>
@@ -1041,10 +1103,10 @@
     </row>
     <row r="17" spans="1:4" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A17" s="15" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C17" s="15" t="s">
         <v>51</v>
@@ -1055,7 +1117,7 @@
     </row>
     <row r="18" spans="1:4" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A18" s="15" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B18" s="15" t="s">
         <v>34</v>
@@ -1069,10 +1131,10 @@
     </row>
     <row r="19" spans="1:4" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A19" s="15" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C19" s="15" t="s">
         <v>51</v>
@@ -1083,7 +1145,7 @@
     </row>
     <row r="20" spans="1:4" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A20" s="15" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B20" s="15" t="s">
         <v>30</v>
@@ -1949,415 +2011,406 @@
         <v>60</v>
       </c>
     </row>
-    <row r="82" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="7" t="s">
+    <row r="82" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A82" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A83" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A84" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A85" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A86" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B82" s="7" t="s">
+      <c r="B86" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="C82" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="D82" s="7" t="s">
+      <c r="C86" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D86" s="7" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="83" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="7" t="s">
+    <row r="87" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A87" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B83" s="7" t="s">
+      <c r="B87" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="C83" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="D83" s="7" t="s">
+      <c r="C87" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D87" s="7" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="84" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="7" t="s">
+    <row r="88" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A88" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B84" s="7" t="s">
+      <c r="B88" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C88" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D88" s="7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A89" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B89" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="C89" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D89" s="7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B90" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="C90" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D90" s="7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A91" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B91" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C91" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D91" s="7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A92" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A93" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B93" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C93" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D93" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A94" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B94" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C94" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D94" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A95" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B95" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="C84" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="D84" s="7" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B85" s="7" t="s">
+      <c r="C95" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D95" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A96" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B96" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C96" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D96" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A97" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B97" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C97" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D97" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A98" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B98" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C85" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="D85" s="7" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B86" s="6" t="s">
+      <c r="C98" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D98" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A99" t="s">
+        <v>120</v>
+      </c>
+      <c r="B99" t="s">
+        <v>76</v>
+      </c>
+      <c r="C99" t="s">
+        <v>52</v>
+      </c>
+      <c r="D99" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A100" t="s">
+        <v>120</v>
+      </c>
+      <c r="B100" t="s">
+        <v>47</v>
+      </c>
+      <c r="C100" t="s">
+        <v>52</v>
+      </c>
+      <c r="D100" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A101" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A102" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A103" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A104" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A105" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A106" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B106" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="C86" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="D86" s="6" t="s">
+      <c r="C106" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D106" s="5" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="87" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B87" s="6" t="s">
+    <row r="107" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A107" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B107" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="C87" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="D87" s="6" t="s">
+      <c r="C107" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D107" s="5" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="88" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B88" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C88" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="D88" s="6" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B89" s="6" t="s">
+    <row r="108" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A108" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B108" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C108" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D108" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A109" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B109" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C109" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D109" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A110" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B110" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C89" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="D89" s="6" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B90" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C90" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="D90" s="6" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B91" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="C91" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="D91" s="6" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D92" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D93" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D94" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B95" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C95" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B96" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C96" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D96" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B97" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="C97" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D97" s="5" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B98" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="C98" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D98" s="5" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B99" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C99" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D99" s="5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B100" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="C100" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D100" s="5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B101" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="C101" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D101" s="5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A102" t="s">
-        <v>68</v>
-      </c>
-      <c r="B102" t="s">
-        <v>66</v>
-      </c>
-      <c r="C102" t="s">
-        <v>52</v>
-      </c>
-      <c r="D102" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B103" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C103" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D103" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A104" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B104" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C104" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D104" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A105" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B105" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C105" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D105" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A106" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B106" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C106" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D106" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A107" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B107" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C107" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D107" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B108" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C108" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D108" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A109" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B109" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C109" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D109" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A110" t="s">
-        <v>64</v>
-      </c>
-      <c r="B110" t="s">
-        <v>65</v>
-      </c>
-      <c r="C110" t="s">
-        <v>52</v>
-      </c>
-      <c r="D110" t="s">
+      <c r="C110" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D110" s="5" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B111" t="s">
         <v>66</v>
@@ -2369,861 +2422,1360 @@
         <v>59</v>
       </c>
     </row>
-    <row r="112" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="10" t="s">
+    <row r="112" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A112" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B112" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C112" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D112" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A113" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B113" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C113" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D113" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A114" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B114" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C114" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D114" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A115" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B115" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C115" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D115" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A116" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D116" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A117" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D117" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A118" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C118" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D118" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A119" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C119" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D119" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A120" t="s">
+        <v>64</v>
+      </c>
+      <c r="B120" t="s">
+        <v>65</v>
+      </c>
+      <c r="C120" t="s">
+        <v>52</v>
+      </c>
+      <c r="D120" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A121" t="s">
+        <v>64</v>
+      </c>
+      <c r="B121" t="s">
+        <v>66</v>
+      </c>
+      <c r="C121" t="s">
+        <v>52</v>
+      </c>
+      <c r="D121" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A122" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B112" s="10" t="s">
+      <c r="B122" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C112" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="D112" s="10" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="10" t="s">
+      <c r="C122" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A123" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B113" s="10" t="s">
+      <c r="B123" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C113" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="D113" s="10" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A114" s="10" t="s">
+      <c r="C123" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A124" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B114" s="10" t="s">
+      <c r="B124" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C114" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="D114" s="10" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A115" s="9" t="s">
+      <c r="C124" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A125" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B115" s="9" t="s">
+      <c r="B125" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="C115" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="D115" s="9" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A116" s="9" t="s">
+      <c r="C125" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D125" s="9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A126" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B116" s="9" t="s">
+      <c r="B126" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="C116" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="D116" s="9" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A117" s="9" t="s">
+      <c r="C126" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D126" s="9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A127" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B117" s="9" t="s">
+      <c r="B127" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="C117" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="D117" s="9" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A118" s="8" t="s">
+      <c r="C127" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D127" s="9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A128" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B118" s="8" t="s">
+      <c r="B128" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="C118" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="D118" s="8" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A119" s="8" t="s">
+      <c r="C128" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D128" s="8" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A129" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B119" s="8" t="s">
+      <c r="B129" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="C119" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="D119" s="8" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="120" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A120" s="8" t="s">
+      <c r="C129" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D129" s="8" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A130" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B120" s="8" t="s">
+      <c r="B130" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="C120" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="D120" s="8" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="121" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A121" s="8" t="s">
+      <c r="C130" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D130" s="8" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A131" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B121" s="8" t="s">
+      <c r="B131" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C121" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="D121" s="8" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="122" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A122" s="7" t="s">
+      <c r="C131" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D131" s="8" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A132" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B122" s="7" t="s">
+      <c r="B132" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="C122" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="D122" s="7" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="123" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A123" s="7" t="s">
+      <c r="C132" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D132" s="7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A133" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B123" s="7" t="s">
+      <c r="B133" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="C123" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="D123" s="7" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="124" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A124" s="7" t="s">
+      <c r="C133" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D133" s="7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A134" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B124" s="7" t="s">
+      <c r="B134" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C124" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="D124" s="7" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="125" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A125" s="7" t="s">
+      <c r="C134" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D134" s="7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A135" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B125" s="7" t="s">
+      <c r="B135" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C125" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="D125" s="7" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="126" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A126" s="6" t="s">
+      <c r="C135" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D135" s="7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A136" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B136" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C136" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D136" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A137" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B137" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C137" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D137" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A138" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B138" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C138" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D138" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A139" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B139" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C139" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D139" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A140" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D140" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A141" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D141" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A142" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D142" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A143" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D143" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A144" t="s">
+        <v>63</v>
+      </c>
+      <c r="B144" t="s">
+        <v>45</v>
+      </c>
+      <c r="C144" t="s">
+        <v>52</v>
+      </c>
+      <c r="D144" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A145" t="s">
+        <v>63</v>
+      </c>
+      <c r="B145" t="s">
+        <v>48</v>
+      </c>
+      <c r="C145" t="s">
+        <v>52</v>
+      </c>
+      <c r="D145" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A146" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B146" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C146" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D146" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A147" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B147" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C147" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D147" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A148" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B148" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C148" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D148" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A149" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B149" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C149" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D149" s="5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A150" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B150" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C150" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D150" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A151" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B151" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C151" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D151" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A152" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B152" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C152" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D152" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A153" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B153" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C153" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D153" s="4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A154" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B154" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C154" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D154" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A155" t="s">
+        <v>116</v>
+      </c>
+      <c r="B155" t="s">
+        <v>45</v>
+      </c>
+      <c r="C155" t="s">
+        <v>52</v>
+      </c>
+      <c r="D155" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A156" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="B126" s="6" t="s">
+      <c r="B156" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C156" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D156" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A157" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B157" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C157" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D157" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A158" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B158" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C158" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D158" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A159" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B159" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C126" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="D126" s="6" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="127" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A127" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="B127" s="6" t="s">
+      <c r="C159" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D159" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A160" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B160" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C160" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D160" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A161" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B161" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="C127" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="D127" s="6" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="128" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A128" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="B128" s="6" t="s">
+      <c r="C161" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D161" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A162" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="B162" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="C162" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="D162" s="21" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A163" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B163" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C163" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D163" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A164" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B164" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="C128" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="D128" s="6" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="129" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A129" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="B129" s="6" t="s">
+      <c r="C164" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D164" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A165" t="s">
+        <v>104</v>
+      </c>
+      <c r="B165" t="s">
+        <v>50</v>
+      </c>
+      <c r="C165" t="s">
+        <v>52</v>
+      </c>
+      <c r="D165" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A166" t="s">
+        <v>104</v>
+      </c>
+      <c r="B166" t="s">
+        <v>45</v>
+      </c>
+      <c r="C166" t="s">
+        <v>52</v>
+      </c>
+      <c r="D166" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A167" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C167" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D167" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A168" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B168" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C129" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="D129" s="6" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="130" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A130" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B130" s="2" t="s">
+      <c r="C168" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D168" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A169" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C169" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D169" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A170" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B170" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C130" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D130" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="131" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A131" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B131" s="2" t="s">
+      <c r="C170" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D170" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A171" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B171" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C171" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D171" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A172" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B172" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C172" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D172" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A173" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B173" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C173" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D173" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A174" t="s">
+        <v>112</v>
+      </c>
+      <c r="B174" t="s">
         <v>45</v>
       </c>
-      <c r="C131" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D131" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A132" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B132" s="2" t="s">
+      <c r="C174" t="s">
+        <v>52</v>
+      </c>
+      <c r="D174" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A175" t="s">
+        <v>112</v>
+      </c>
+      <c r="B175" t="s">
+        <v>38</v>
+      </c>
+      <c r="C175" t="s">
+        <v>52</v>
+      </c>
+      <c r="D175" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A176" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B176" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C176" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D176" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A177" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B177" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C177" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D177" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A178" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B178" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C178" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D178" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A179" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B179" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C179" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D179" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A180" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B180" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C180" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D180" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A181" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B181" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C132" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D132" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="133" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A133" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B133" s="2" t="s">
+      <c r="C181" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D181" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A182" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B182" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C182" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D182" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A183" t="s">
+        <v>87</v>
+      </c>
+      <c r="B183" t="s">
+        <v>48</v>
+      </c>
+      <c r="C183" t="s">
+        <v>52</v>
+      </c>
+      <c r="D183" t="s">
+        <v>67</v>
+      </c>
+      <c r="E183" s="12">
+        <v>35977</v>
+      </c>
+      <c r="F183" s="12">
+        <v>36012</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A184" t="s">
+        <v>87</v>
+      </c>
+      <c r="B184" t="s">
+        <v>45</v>
+      </c>
+      <c r="C184" t="s">
+        <v>52</v>
+      </c>
+      <c r="D184" t="s">
+        <v>67</v>
+      </c>
+      <c r="E184" s="12">
+        <v>35977</v>
+      </c>
+      <c r="F184" s="12">
+        <v>36012</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A185" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="B185" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C185" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D185" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A186" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="B186" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C186" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D186" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A187" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="B187" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C133" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D133" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A134" t="s">
-        <v>63</v>
-      </c>
-      <c r="B134" t="s">
+      <c r="C187" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D187" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A188" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="B188" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="C188" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D188" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A189" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B189" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C189" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D189" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A190" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B190" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C190" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D190" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A191" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B191" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C134" t="s">
-        <v>52</v>
-      </c>
-      <c r="D134" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A135" t="s">
-        <v>63</v>
-      </c>
-      <c r="B135" t="s">
+      <c r="C191" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D191" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A192" t="s">
+        <v>114</v>
+      </c>
+      <c r="B192" t="s">
         <v>48</v>
       </c>
-      <c r="C135" t="s">
-        <v>52</v>
-      </c>
-      <c r="D135" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="136" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A136" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="B136" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C136" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D136" s="5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="137" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A137" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="B137" s="5" t="s">
+      <c r="C192" t="s">
+        <v>52</v>
+      </c>
+      <c r="D192" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A193" t="s">
+        <v>114</v>
+      </c>
+      <c r="B193" t="s">
+        <v>73</v>
+      </c>
+      <c r="C193" t="s">
+        <v>52</v>
+      </c>
+      <c r="D193" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" s="22" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A194" s="22" t="s">
+        <v>117</v>
+      </c>
+      <c r="B194" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="C137" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D137" s="5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A138" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="B138" s="5" t="s">
+      <c r="C194" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="D194" s="22" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" s="22" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A195" s="22" t="s">
+        <v>117</v>
+      </c>
+      <c r="B195" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="C195" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="D195" s="22" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" s="22" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A196" s="22" t="s">
+        <v>117</v>
+      </c>
+      <c r="B196" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="C138" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D138" s="5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A139" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="B139" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C139" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D139" s="5" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="140" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A140" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="B140" s="5" t="s">
+      <c r="C196" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="D196" s="22" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A197" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B197" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C197" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D197" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A198" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B198" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C140" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D140" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E140" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="141" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A141" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B141" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C141" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D141" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A142" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B142" s="4" t="s">
+      <c r="C198" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D198" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A199" t="s">
+        <v>113</v>
+      </c>
+      <c r="B199" t="s">
+        <v>73</v>
+      </c>
+      <c r="C199" t="s">
+        <v>52</v>
+      </c>
+      <c r="D199" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A200" t="s">
+        <v>113</v>
+      </c>
+      <c r="B200" t="s">
+        <v>38</v>
+      </c>
+      <c r="C200" t="s">
+        <v>52</v>
+      </c>
+      <c r="D200" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A201" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B201" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C142" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D142" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="143" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A143" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B143" s="4" t="s">
+      <c r="C201" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D201" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A202" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B202" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C202" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D202" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A203" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B203" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C203" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D203" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A204" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B204" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C143" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D143" s="4" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="144" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A144" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B144" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C144" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D144" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E144" s="4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="145" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A145" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="B145" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C145" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D145" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E145" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="146" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A146" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="B146" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C146" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D146" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="147" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A147" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="B147" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C147" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D147" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="148" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A148" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B148" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C148" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="D148" s="8" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="149" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A149" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B149" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="C149" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="D149" s="8" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="150" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A150" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B150" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="C150" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="D150" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="E150" s="8" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="151" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A151" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="B151" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="C151" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="D151" s="7" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="152" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A152" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B152" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C152" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="D152" s="6" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="153" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A153" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B153" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C153" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="D153" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="E153" s="6" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="154" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A154" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="B154" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C154" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D154" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="E154" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="155" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A155" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="B155" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C155" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D155" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="156" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A156" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="B156" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C156" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D156" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E156" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="157" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A157" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="B157" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C157" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D157" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="158" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A158" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B158" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C158" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D158" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E158" s="3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="159" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A159" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B159" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C159" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D159" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="160" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A160" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B160" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C160" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D160" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="161" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A161" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B161" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C161" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D161" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E161" s="4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="162" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A162" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B162" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C162" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D162" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="163" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A163" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B163" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C163" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D163" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="164" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A164" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B164" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C164" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D164" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E164" s="5" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="165" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A165" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B165" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C165" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D165" s="5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="166" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A166" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B166" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="C166" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D166" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E166" s="5" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="167" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A167" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B167" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C167" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D167" s="5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A168" t="s">
-        <v>88</v>
-      </c>
-      <c r="B168" t="s">
-        <v>48</v>
-      </c>
-      <c r="C168" t="s">
-        <v>52</v>
-      </c>
-      <c r="D168" t="s">
-        <v>67</v>
-      </c>
-      <c r="E168" s="12">
-        <v>35977</v>
-      </c>
-      <c r="F168" s="12">
-        <v>36012</v>
-      </c>
-    </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A169" t="s">
-        <v>88</v>
-      </c>
-      <c r="B169" t="s">
-        <v>45</v>
-      </c>
-      <c r="C169" t="s">
-        <v>52</v>
-      </c>
-      <c r="D169" t="s">
-        <v>67</v>
-      </c>
-      <c r="E169" s="12">
-        <v>35977</v>
-      </c>
-      <c r="F169" s="12">
-        <v>36012</v>
+      <c r="C204" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D204" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A205" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B205" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C205" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D205" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A206" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B206" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C206" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D206" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A207" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B207" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C207" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D207" s="2" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
